--- a/data/fmsForecastOutput/File1/RPT_RPT8057223817206DA_fmsForecastOutput.xlsx
+++ b/data/fmsForecastOutput/File1/RPT_RPT8057223817206DA_fmsForecastOutput.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="FMS Forecast Output" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FMS Forecast Output" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1878,7 +1878,7 @@
         <v>245.8826609986716</v>
       </c>
       <c r="D8" s="149" t="n">
-        <v>270.3380899851418</v>
+        <v>270.3380899851417</v>
       </c>
       <c r="E8" s="149" t="n">
         <v>296.6761486807943</v>
@@ -1887,25 +1887,25 @@
         <v>323.6944370668982</v>
       </c>
       <c r="G8" s="150" t="n">
-        <v>348.6721921705754</v>
+        <v>348.6721921705753</v>
       </c>
       <c r="H8" s="148" t="n">
-        <v>37.09946383014145</v>
+        <v>37.09946383014143</v>
       </c>
       <c r="I8" s="149" t="n">
-        <v>42.25355911349474</v>
+        <v>42.25355911349473</v>
       </c>
       <c r="J8" s="149" t="n">
-        <v>46.92306984755227</v>
+        <v>46.92306984755226</v>
       </c>
       <c r="K8" s="149" t="n">
-        <v>53.48188141829421</v>
+        <v>53.48188141829419</v>
       </c>
       <c r="L8" s="150" t="n">
-        <v>58.51947333720743</v>
+        <v>58.51947333720742</v>
       </c>
       <c r="M8" s="151" t="n">
-        <v>9538896.079221018</v>
+        <v>9538896.079221016</v>
       </c>
       <c r="N8" s="152" t="n">
         <v>11170719.1322164</v>
@@ -1917,7 +1917,7 @@
         <v>14586124.87895032</v>
       </c>
       <c r="Q8" s="153" t="n">
-        <v>16205988.39904837</v>
+        <v>16205988.39904836</v>
       </c>
       <c r="S8" s="21" t="inlineStr">
         <is>
@@ -1925,37 +1925,37 @@
         </is>
       </c>
       <c r="T8" s="148" t="n">
-        <v>343.441606756159</v>
+        <v>343.4416067561589</v>
       </c>
       <c r="U8" s="149" t="n">
         <v>377.6002244924043</v>
       </c>
       <c r="V8" s="149" t="n">
-        <v>414.3884435580903</v>
+        <v>414.3884435580902</v>
       </c>
       <c r="W8" s="149" t="n">
-        <v>452.1267872763362</v>
+        <v>452.1267872763361</v>
       </c>
       <c r="X8" s="150" t="n">
-        <v>487.0149746382547</v>
+        <v>487.0149746382546</v>
       </c>
       <c r="Y8" s="148" t="n">
-        <v>46.90519357709751</v>
+        <v>46.90519357709749</v>
       </c>
       <c r="Z8" s="149" t="n">
         <v>53.4538981632904</v>
       </c>
       <c r="AA8" s="149" t="n">
-        <v>59.37354250509094</v>
+        <v>59.37354250509092</v>
       </c>
       <c r="AB8" s="149" t="n">
-        <v>67.72610700365402</v>
+        <v>67.72610700365401</v>
       </c>
       <c r="AC8" s="150" t="n">
-        <v>74.12705611135367</v>
+        <v>74.12705611135365</v>
       </c>
       <c r="AD8" s="151" t="n">
-        <v>9538896.079221018</v>
+        <v>9538896.079221016</v>
       </c>
       <c r="AE8" s="152" t="n">
         <v>11170719.1322164</v>
@@ -1967,7 +1967,7 @@
         <v>14586124.87895032</v>
       </c>
       <c r="AH8" s="153" t="n">
-        <v>16205988.39904837</v>
+        <v>16205988.39904836</v>
       </c>
       <c r="AQ8" s="28" t="inlineStr">
         <is>
@@ -2031,7 +2031,7 @@
         <v>753.2311592282184</v>
       </c>
       <c r="F9" s="156" t="n">
-        <v>798.8860516383605</v>
+        <v>798.8860516383604</v>
       </c>
       <c r="G9" s="157" t="n">
         <v>842.0000221873738</v>
@@ -2046,7 +2046,7 @@
         <v>27.66756061956131</v>
       </c>
       <c r="K9" s="156" t="n">
-        <v>32.25690910457772</v>
+        <v>32.25690910457771</v>
       </c>
       <c r="L9" s="157" t="n">
         <v>36.37825922566281</v>
@@ -2061,7 +2061,7 @@
         <v>6816666.058827664</v>
       </c>
       <c r="P9" s="159" t="n">
-        <v>8008723.280544685</v>
+        <v>8008723.280544683</v>
       </c>
       <c r="Q9" s="160" t="n">
         <v>9107005.630963489</v>
@@ -2081,7 +2081,7 @@
         <v>884.541583767431</v>
       </c>
       <c r="W9" s="156" t="n">
-        <v>938.1554715420378</v>
+        <v>938.1554715420376</v>
       </c>
       <c r="X9" s="157" t="n">
         <v>988.7854797735109</v>
@@ -2096,7 +2096,7 @@
         <v>28.73423950043177</v>
       </c>
       <c r="AB9" s="156" t="n">
-        <v>33.51518823618823</v>
+        <v>33.51518823618822</v>
       </c>
       <c r="AC9" s="157" t="n">
         <v>37.81014062994691</v>
@@ -2111,7 +2111,7 @@
         <v>6816666.058827664</v>
       </c>
       <c r="AG9" s="159" t="n">
-        <v>8008723.280544685</v>
+        <v>8008723.280544683</v>
       </c>
       <c r="AH9" s="160" t="n">
         <v>9107005.630963489</v>
@@ -2170,7 +2170,7 @@
         </is>
       </c>
       <c r="C10" s="161" t="n">
-        <v>311.5498020041764</v>
+        <v>311.5498020041763</v>
       </c>
       <c r="D10" s="162" t="n">
         <v>342.5482281064815</v>
@@ -2179,7 +2179,7 @@
         <v>376.6659214282823</v>
       </c>
       <c r="F10" s="162" t="n">
-        <v>410.1720905724645</v>
+        <v>410.1720905724644</v>
       </c>
       <c r="G10" s="163" t="n">
         <v>441.8005251797444</v>
@@ -2194,7 +2194,7 @@
         <v>37.72448948385853</v>
       </c>
       <c r="K10" s="162" t="n">
-        <v>43.36743762355332</v>
+        <v>43.36743762355331</v>
       </c>
       <c r="L10" s="163" t="n">
         <v>48.00717341811047</v>
@@ -2209,7 +2209,7 @@
         <v>19456231.33906148</v>
       </c>
       <c r="P10" s="165" t="n">
-        <v>22594848.15949501</v>
+        <v>22594848.159495</v>
       </c>
       <c r="Q10" s="166" t="n">
         <v>25312994.03001186</v>
@@ -2220,22 +2220,22 @@
         </is>
       </c>
       <c r="T10" s="161" t="n">
-        <v>422.1895158958978</v>
+        <v>422.1895158958977</v>
       </c>
       <c r="U10" s="162" t="n">
-        <v>463.7148793872863</v>
+        <v>463.7148793872861</v>
       </c>
       <c r="V10" s="162" t="n">
         <v>509.216500523625</v>
       </c>
       <c r="W10" s="162" t="n">
-        <v>553.8250521348414</v>
+        <v>553.8250521348411</v>
       </c>
       <c r="X10" s="163" t="n">
-        <v>595.7897406975155</v>
+        <v>595.7897406975154</v>
       </c>
       <c r="Y10" s="161" t="n">
-        <v>33.53282166694908</v>
+        <v>33.53282166694907</v>
       </c>
       <c r="Z10" s="162" t="n">
         <v>38.47335192991716</v>
@@ -2259,7 +2259,7 @@
         <v>19456231.33906148</v>
       </c>
       <c r="AG10" s="165" t="n">
-        <v>22594848.15949501</v>
+        <v>22594848.159495</v>
       </c>
       <c r="AH10" s="166" t="n">
         <v>25312994.03001186</v>
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="C12" s="161" t="n">
-        <v>313.504717764103</v>
+        <v>313.5047177641029</v>
       </c>
       <c r="D12" s="162" t="n">
         <v>344.7396021103198</v>
@@ -2470,13 +2470,13 @@
         <v>379.0419267878169</v>
       </c>
       <c r="F12" s="162" t="n">
-        <v>412.7770831439194</v>
+        <v>412.7770831439193</v>
       </c>
       <c r="G12" s="163" t="n">
-        <v>444.7284190547479</v>
+        <v>444.7284190547478</v>
       </c>
       <c r="H12" s="161" t="n">
-        <v>29.35563898585155</v>
+        <v>29.35563898585154</v>
       </c>
       <c r="I12" s="162" t="n">
         <v>33.67203751225355</v>
@@ -2485,13 +2485,13 @@
         <v>37.8226422781201</v>
       </c>
       <c r="K12" s="162" t="n">
-        <v>43.49246542631729</v>
+        <v>43.49246542631727</v>
       </c>
       <c r="L12" s="163" t="n">
         <v>48.17570812790434</v>
       </c>
       <c r="M12" s="164" t="n">
-        <v>14570039.51031477</v>
+        <v>14570039.51031476</v>
       </c>
       <c r="N12" s="165" t="n">
         <v>17182119.93539887</v>
@@ -2500,7 +2500,7 @@
         <v>19654142.52516668</v>
       </c>
       <c r="P12" s="165" t="n">
-        <v>22831112.15123956</v>
+        <v>22831112.15123955</v>
       </c>
       <c r="Q12" s="166" t="n">
         <v>25593675.84123728</v>
@@ -2511,10 +2511,10 @@
         </is>
       </c>
       <c r="T12" s="161" t="n">
-        <v>424.458089526371</v>
+        <v>424.4580895263709</v>
       </c>
       <c r="U12" s="162" t="n">
-        <v>466.2584514205112</v>
+        <v>466.2584514205111</v>
       </c>
       <c r="V12" s="162" t="n">
         <v>511.9475785654568</v>
@@ -2535,13 +2535,13 @@
         <v>43.29697330978944</v>
       </c>
       <c r="AB12" s="162" t="n">
-        <v>49.82893673885562</v>
+        <v>49.8289367388556</v>
       </c>
       <c r="AC12" s="163" t="n">
-        <v>55.23104365794649</v>
+        <v>55.23104365794648</v>
       </c>
       <c r="AD12" s="164" t="n">
-        <v>14570039.51031477</v>
+        <v>14570039.51031476</v>
       </c>
       <c r="AE12" s="165" t="n">
         <v>17182119.93539887</v>
@@ -2550,7 +2550,7 @@
         <v>19654142.52516668</v>
       </c>
       <c r="AG12" s="165" t="n">
-        <v>22831112.15123956</v>
+        <v>22831112.15123955</v>
       </c>
       <c r="AH12" s="166" t="n">
         <v>25593675.84123728</v>
@@ -2603,49 +2603,49 @@
         </is>
       </c>
       <c r="C13" s="155" t="n">
-        <v>3805.200098079478</v>
+        <v>3805.200098079476</v>
       </c>
       <c r="D13" s="156" t="n">
-        <v>4145.287101500089</v>
+        <v>4145.287101500087</v>
       </c>
       <c r="E13" s="156" t="n">
-        <v>4247.998455488952</v>
+        <v>4247.998455488949</v>
       </c>
       <c r="F13" s="156" t="n">
         <v>4651.363530807002</v>
       </c>
       <c r="G13" s="157" t="n">
-        <v>5074.819930847302</v>
+        <v>5074.819930847299</v>
       </c>
       <c r="H13" s="155" t="n">
-        <v>3790.9693894778</v>
+        <v>3790.969389477798</v>
       </c>
       <c r="I13" s="156" t="n">
-        <v>4126.531525489155</v>
+        <v>4126.531525489153</v>
       </c>
       <c r="J13" s="156" t="n">
-        <v>3951.72312617023</v>
+        <v>3951.723126170228</v>
       </c>
       <c r="K13" s="156" t="n">
-        <v>4265.64333278015</v>
+        <v>4265.643332780148</v>
       </c>
       <c r="L13" s="157" t="n">
         <v>4665.144903435877</v>
       </c>
       <c r="M13" s="158" t="n">
-        <v>1898653.394745209</v>
+        <v>1898653.394745208</v>
       </c>
       <c r="N13" s="159" t="n">
-        <v>2205194.566085306</v>
+        <v>2205194.566085305</v>
       </c>
       <c r="O13" s="159" t="n">
-        <v>2364673.018946982</v>
+        <v>2364673.018946981</v>
       </c>
       <c r="P13" s="159" t="n">
-        <v>2738987.489065457</v>
+        <v>2738987.489065456</v>
       </c>
       <c r="Q13" s="160" t="n">
-        <v>3230542.393035219</v>
+        <v>3230542.393035218</v>
       </c>
       <c r="S13" s="32" t="inlineStr">
         <is>
@@ -2653,49 +2653,49 @@
         </is>
       </c>
       <c r="T13" s="155" t="n">
-        <v>3110.155067973367</v>
+        <v>3110.155067973365</v>
       </c>
       <c r="U13" s="156" t="n">
-        <v>3388.122925110324</v>
+        <v>3388.122925110322</v>
       </c>
       <c r="V13" s="156" t="n">
-        <v>3472.07336921656</v>
+        <v>3472.073369216558</v>
       </c>
       <c r="W13" s="156" t="n">
-        <v>3801.761138823491</v>
+        <v>3801.76113882349</v>
       </c>
       <c r="X13" s="157" t="n">
-        <v>4147.870419467052</v>
+        <v>4147.87041946705</v>
       </c>
       <c r="Y13" s="155" t="n">
-        <v>3100.641741933631</v>
+        <v>3100.64174193363</v>
       </c>
       <c r="Z13" s="156" t="n">
-        <v>3375.582895546293</v>
+        <v>3375.582895546292</v>
       </c>
       <c r="AA13" s="156" t="n">
-        <v>3271.592590513333</v>
+        <v>3271.59259051333</v>
       </c>
       <c r="AB13" s="156" t="n">
-        <v>3540.117566446097</v>
+        <v>3540.117566446096</v>
       </c>
       <c r="AC13" s="157" t="n">
-        <v>3870.090995076565</v>
+        <v>3870.090995076563</v>
       </c>
       <c r="AD13" s="158" t="n">
-        <v>1898653.394745209</v>
+        <v>1898653.394745208</v>
       </c>
       <c r="AE13" s="159" t="n">
-        <v>2205194.566085306</v>
+        <v>2205194.566085305</v>
       </c>
       <c r="AF13" s="159" t="n">
-        <v>2364673.018946982</v>
+        <v>2364673.018946981</v>
       </c>
       <c r="AG13" s="159" t="n">
-        <v>2738987.489065457</v>
+        <v>2738987.489065456</v>
       </c>
       <c r="AH13" s="160" t="n">
-        <v>3230542.393035219</v>
+        <v>3230542.393035218</v>
       </c>
       <c r="AJ13" s="39" t="n"/>
       <c r="AQ13" s="49" t="inlineStr">
@@ -2752,10 +2752,10 @@
         <v>384.8763347858916</v>
       </c>
       <c r="E14" s="168" t="n">
-        <v>420.1357219241933</v>
+        <v>420.1357219241931</v>
       </c>
       <c r="F14" s="168" t="n">
-        <v>457.4269465660445</v>
+        <v>457.4269465660444</v>
       </c>
       <c r="G14" s="169" t="n">
         <v>495.3841975152899</v>
@@ -2767,10 +2767,10 @@
         <v>37.95384020239865</v>
       </c>
       <c r="J14" s="168" t="n">
-        <v>42.3245056160499</v>
+        <v>42.32450561604989</v>
       </c>
       <c r="K14" s="168" t="n">
-        <v>48.65063146587014</v>
+        <v>48.65063146587013</v>
       </c>
       <c r="L14" s="169" t="n">
         <v>54.1860198650076</v>
@@ -2782,7 +2782,7 @@
         <v>19387314.50148417</v>
       </c>
       <c r="O14" s="171" t="n">
-        <v>22018815.54411366</v>
+        <v>22018815.54411365</v>
       </c>
       <c r="P14" s="171" t="n">
         <v>25570099.64030501</v>
@@ -2802,10 +2802,10 @@
         <v>516.968528774744</v>
       </c>
       <c r="V14" s="168" t="n">
-        <v>563.5448716067364</v>
+        <v>563.5448716067361</v>
       </c>
       <c r="W14" s="168" t="n">
-        <v>612.8195926529053</v>
+        <v>612.8195926529052</v>
       </c>
       <c r="X14" s="169" t="n">
         <v>662.6368851858587</v>
@@ -2817,10 +2817,10 @@
         <v>43.41607340593965</v>
       </c>
       <c r="AA14" s="168" t="n">
-        <v>48.42910334268922</v>
+        <v>48.42910334268921</v>
       </c>
       <c r="AB14" s="168" t="n">
-        <v>55.71270456749252</v>
+        <v>55.71270456749251</v>
       </c>
       <c r="AC14" s="169" t="n">
         <v>62.09069160254662</v>
@@ -2832,7 +2832,7 @@
         <v>19387314.50148417</v>
       </c>
       <c r="AF14" s="171" t="n">
-        <v>22018815.54411366</v>
+        <v>22018815.54411365</v>
       </c>
       <c r="AG14" s="171" t="n">
         <v>25570099.64030501</v>
@@ -3840,19 +3840,19 @@
         </is>
       </c>
       <c r="C24" s="79" t="n">
-        <v>498.9628260819919</v>
+        <v>498.962826081992</v>
       </c>
       <c r="D24" s="80" t="n">
         <v>531.9763172223448</v>
       </c>
       <c r="E24" s="80" t="n">
-        <v>556.6558094887075</v>
+        <v>556.6558094887076</v>
       </c>
       <c r="F24" s="80" t="n">
         <v>588.8568956015889</v>
       </c>
       <c r="G24" s="81" t="n">
-        <v>636.5826644209308</v>
+        <v>636.5826644209309</v>
       </c>
       <c r="H24" s="79" t="n">
         <v>1.87302873</v>
@@ -3870,19 +3870,19 @@
         <v>55.90223367</v>
       </c>
       <c r="M24" s="79" t="n">
-        <v>500.8358548119919</v>
+        <v>500.835854811992</v>
       </c>
       <c r="N24" s="80" t="n">
         <v>534.3942127823449</v>
       </c>
       <c r="O24" s="80" t="n">
-        <v>598.3903586987075</v>
+        <v>598.3903586987076</v>
       </c>
       <c r="P24" s="80" t="n">
         <v>642.1041975115889</v>
       </c>
       <c r="Q24" s="81" t="n">
-        <v>692.4848980909308</v>
+        <v>692.4848980909309</v>
       </c>
       <c r="S24" s="32" t="inlineStr">
         <is>
@@ -3890,19 +3890,19 @@
         </is>
       </c>
       <c r="T24" s="79" t="n">
-        <v>610.469045192144</v>
+        <v>610.4690451921441</v>
       </c>
       <c r="U24" s="80" t="n">
         <v>650.8602594498547</v>
       </c>
       <c r="V24" s="80" t="n">
-        <v>681.0550260579738</v>
+        <v>681.055026057974</v>
       </c>
       <c r="W24" s="80" t="n">
         <v>720.452282258079</v>
       </c>
       <c r="X24" s="81" t="n">
-        <v>778.8436152376966</v>
+        <v>778.8436152376967</v>
       </c>
       <c r="Y24" s="79" t="n">
         <v>1.87302873</v>
@@ -3920,19 +3920,19 @@
         <v>55.90223367</v>
       </c>
       <c r="AD24" s="79" t="n">
-        <v>612.342073922144</v>
+        <v>612.3420739221441</v>
       </c>
       <c r="AE24" s="80" t="n">
         <v>653.2781550098547</v>
       </c>
       <c r="AF24" s="80" t="n">
-        <v>722.7895752679738</v>
+        <v>722.789575267974</v>
       </c>
       <c r="AG24" s="80" t="n">
         <v>773.699584168079</v>
       </c>
       <c r="AH24" s="81" t="n">
-        <v>834.7458489076965</v>
+        <v>834.7458489076967</v>
       </c>
     </row>
     <row r="25" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -4408,13 +4408,13 @@
         </is>
       </c>
       <c r="C35" s="148" t="n">
-        <v>252.4498024009513</v>
+        <v>252.4498024009512</v>
       </c>
       <c r="D35" s="149" t="n">
         <v>284.3056120885323</v>
       </c>
       <c r="E35" s="149" t="n">
-        <v>313.9988433736507</v>
+        <v>313.9988433736506</v>
       </c>
       <c r="F35" s="149" t="n">
         <v>346.9583558469386</v>
@@ -4423,34 +4423,34 @@
         <v>374.7258202030196</v>
       </c>
       <c r="H35" s="148" t="n">
-        <v>38.09033249868337</v>
+        <v>38.09033249868335</v>
       </c>
       <c r="I35" s="149" t="n">
         <v>44.43666812671997</v>
       </c>
       <c r="J35" s="149" t="n">
-        <v>49.66287220994333</v>
+        <v>49.66287220994332</v>
       </c>
       <c r="K35" s="149" t="n">
-        <v>57.32562416776201</v>
+        <v>57.32562416776199</v>
       </c>
       <c r="L35" s="150" t="n">
-        <v>62.89218967426554</v>
+        <v>62.89218967426553</v>
       </c>
       <c r="M35" s="151" t="n">
-        <v>9793665.078057557</v>
+        <v>9793665.078057554</v>
       </c>
       <c r="N35" s="152" t="n">
-        <v>11747875.19038999</v>
+        <v>11747875.19038998</v>
       </c>
       <c r="O35" s="152" t="n">
-        <v>13377579.88428444</v>
+        <v>13377579.88428443</v>
       </c>
       <c r="P35" s="152" t="n">
         <v>15634429.6554371</v>
       </c>
       <c r="Q35" s="153" t="n">
-        <v>17416938.97993196</v>
+        <v>17416938.97993195</v>
       </c>
       <c r="S35" s="21" t="inlineStr">
         <is>
@@ -4458,49 +4458,49 @@
         </is>
       </c>
       <c r="T35" s="148" t="n">
-        <v>352.6143950521421</v>
+        <v>352.614395052142</v>
       </c>
       <c r="U35" s="149" t="n">
         <v>397.1096450188746</v>
       </c>
       <c r="V35" s="149" t="n">
-        <v>438.5842696260908</v>
+        <v>438.5842696260907</v>
       </c>
       <c r="W35" s="149" t="n">
-        <v>484.6211389024763</v>
+        <v>484.6211389024762</v>
       </c>
       <c r="X35" s="150" t="n">
-        <v>523.4059093912274</v>
+        <v>523.4059093912273</v>
       </c>
       <c r="Y35" s="148" t="n">
-        <v>48.15795795450826</v>
+        <v>48.15795795450823</v>
       </c>
       <c r="Z35" s="149" t="n">
         <v>56.2156936030273</v>
       </c>
       <c r="AA35" s="149" t="n">
-        <v>62.84031849710247</v>
+        <v>62.84031849710244</v>
       </c>
       <c r="AB35" s="149" t="n">
-        <v>72.59358222781339</v>
+        <v>72.59358222781336</v>
       </c>
       <c r="AC35" s="150" t="n">
-        <v>79.66600871621331</v>
+        <v>79.6660087162133</v>
       </c>
       <c r="AD35" s="151" t="n">
-        <v>9793665.078057557</v>
+        <v>9793665.078057554</v>
       </c>
       <c r="AE35" s="152" t="n">
-        <v>11747875.19038999</v>
+        <v>11747875.19038998</v>
       </c>
       <c r="AF35" s="152" t="n">
-        <v>13377579.88428444</v>
+        <v>13377579.88428443</v>
       </c>
       <c r="AG35" s="152" t="n">
         <v>15634429.6554371</v>
       </c>
       <c r="AH35" s="153" t="n">
-        <v>17416938.97993196</v>
+        <v>17416938.97993195</v>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1" thickBot="1">
@@ -4519,7 +4519,7 @@
         <v>797.8313589184902</v>
       </c>
       <c r="F36" s="156" t="n">
-        <v>856.9130089426513</v>
+        <v>856.9130089426512</v>
       </c>
       <c r="G36" s="157" t="n">
         <v>905.3998678105236</v>
@@ -4534,7 +4534,7 @@
         <v>29.30580767487365</v>
       </c>
       <c r="K36" s="156" t="n">
-        <v>34.59988440567489</v>
+        <v>34.59988440567488</v>
       </c>
       <c r="L36" s="157" t="n">
         <v>39.11742307147171</v>
@@ -4549,7 +4549,7 @@
         <v>7220293.369940395</v>
       </c>
       <c r="P36" s="159" t="n">
-        <v>8590435.582203966</v>
+        <v>8590435.582203964</v>
       </c>
       <c r="Q36" s="160" t="n">
         <v>9792733.345782664</v>
@@ -4569,7 +4569,7 @@
         <v>936.9169147492228</v>
       </c>
       <c r="W36" s="156" t="n">
-        <v>1006.298240314023</v>
+        <v>1006.298240314022</v>
       </c>
       <c r="X36" s="157" t="n">
         <v>1063.237789892456</v>
@@ -4584,7 +4584,7 @@
         <v>30.43564657044792</v>
       </c>
       <c r="AB36" s="156" t="n">
-        <v>35.9495584355905</v>
+        <v>35.94955843559049</v>
       </c>
       <c r="AC36" s="157" t="n">
         <v>40.65712045864193</v>
@@ -4599,7 +4599,7 @@
         <v>7220293.369940395</v>
       </c>
       <c r="AG36" s="159" t="n">
-        <v>8590435.582203966</v>
+        <v>8590435.582203964</v>
       </c>
       <c r="AH36" s="160" t="n">
         <v>9792733.345782664</v>
@@ -4612,46 +4612,46 @@
         </is>
       </c>
       <c r="C37" s="161" t="n">
-        <v>319.9434062749648</v>
+        <v>319.9434062749647</v>
       </c>
       <c r="D37" s="162" t="n">
-        <v>360.3500327575787</v>
+        <v>360.3500327575786</v>
       </c>
       <c r="E37" s="162" t="n">
         <v>398.7677147520912</v>
       </c>
       <c r="F37" s="162" t="n">
-        <v>439.7623541534582</v>
+        <v>439.7623541534581</v>
       </c>
       <c r="G37" s="163" t="n">
-        <v>474.9042135915143</v>
+        <v>474.9042135915142</v>
       </c>
       <c r="H37" s="161" t="n">
         <v>30.07669660528159</v>
       </c>
       <c r="I37" s="162" t="n">
-        <v>35.33287344021523</v>
+        <v>35.33287344021522</v>
       </c>
       <c r="J37" s="162" t="n">
         <v>39.93806608419665</v>
       </c>
       <c r="K37" s="162" t="n">
-        <v>46.49601204294458</v>
+        <v>46.49601204294456</v>
       </c>
       <c r="L37" s="163" t="n">
-        <v>51.60430474726941</v>
+        <v>51.6043047472694</v>
       </c>
       <c r="M37" s="164" t="n">
         <v>14815649.47122803</v>
       </c>
       <c r="N37" s="165" t="n">
-        <v>17894285.71969355</v>
+        <v>17894285.71969354</v>
       </c>
       <c r="O37" s="165" t="n">
         <v>20597873.25422483</v>
       </c>
       <c r="P37" s="165" t="n">
-        <v>24224865.23764107</v>
+        <v>24224865.23764106</v>
       </c>
       <c r="Q37" s="166" t="n">
         <v>27209672.32571462</v>
@@ -4662,31 +4662,31 @@
         </is>
       </c>
       <c r="T37" s="161" t="n">
-        <v>433.5639147910651</v>
+        <v>433.563914791065</v>
       </c>
       <c r="U37" s="162" t="n">
-        <v>487.8135639500143</v>
+        <v>487.8135639500142</v>
       </c>
       <c r="V37" s="162" t="n">
         <v>539.0960229634836</v>
       </c>
       <c r="W37" s="162" t="n">
-        <v>593.778597602929</v>
+        <v>593.7785976029288</v>
       </c>
       <c r="X37" s="163" t="n">
-        <v>640.4316929155569</v>
+        <v>640.4316929155568</v>
       </c>
       <c r="Y37" s="161" t="n">
-        <v>34.43624459755173</v>
+        <v>34.43624459755172</v>
       </c>
       <c r="Z37" s="162" t="n">
-        <v>40.47276409770218</v>
+        <v>40.47276409770217</v>
       </c>
       <c r="AA37" s="162" t="n">
         <v>45.76150035782853</v>
       </c>
       <c r="AB37" s="162" t="n">
-        <v>53.32028973054803</v>
+        <v>53.32028973054801</v>
       </c>
       <c r="AC37" s="163" t="n">
         <v>59.21763993817228</v>
@@ -4695,13 +4695,13 @@
         <v>14815649.47122803</v>
       </c>
       <c r="AE37" s="165" t="n">
-        <v>17894285.71969355</v>
+        <v>17894285.71969354</v>
       </c>
       <c r="AF37" s="165" t="n">
         <v>20597873.25422483</v>
       </c>
       <c r="AG37" s="165" t="n">
-        <v>24224865.23764107</v>
+        <v>24224865.23764106</v>
       </c>
       <c r="AH37" s="166" t="n">
         <v>27209672.32571462</v>
@@ -4819,13 +4819,13 @@
         <v>321.948742738072</v>
       </c>
       <c r="D39" s="162" t="n">
-        <v>362.6492926804748</v>
+        <v>362.6492926804747</v>
       </c>
       <c r="E39" s="162" t="n">
         <v>401.2746246785175</v>
       </c>
       <c r="F39" s="162" t="n">
-        <v>442.5448236225008</v>
+        <v>442.5448236225007</v>
       </c>
       <c r="G39" s="163" t="n">
         <v>478.0383808327265</v>
@@ -4834,16 +4834,16 @@
         <v>30.14631209115986</v>
       </c>
       <c r="I39" s="162" t="n">
-        <v>35.42134559586075</v>
+        <v>35.42134559586074</v>
       </c>
       <c r="J39" s="162" t="n">
         <v>40.04112872980018</v>
       </c>
       <c r="K39" s="162" t="n">
-        <v>46.62895840631368</v>
+        <v>46.62895840631366</v>
       </c>
       <c r="L39" s="163" t="n">
-        <v>51.7840473471032</v>
+        <v>51.78404734710319</v>
       </c>
       <c r="M39" s="164" t="n">
         <v>14962473.08635233</v>
@@ -4855,7 +4855,7 @@
         <v>20806955.9270134</v>
       </c>
       <c r="P39" s="165" t="n">
-        <v>24477595.56591722</v>
+        <v>24477595.56591721</v>
       </c>
       <c r="Q39" s="166" t="n">
         <v>27510630.83557202</v>
@@ -4866,31 +4866,31 @@
         </is>
       </c>
       <c r="T39" s="161" t="n">
-        <v>435.8905640802652</v>
+        <v>435.8905640802651</v>
       </c>
       <c r="U39" s="162" t="n">
-        <v>490.4812112645882</v>
+        <v>490.4812112645881</v>
       </c>
       <c r="V39" s="162" t="n">
         <v>541.9758552433901</v>
       </c>
       <c r="W39" s="162" t="n">
-        <v>596.9435106132358</v>
+        <v>596.9435106132357</v>
       </c>
       <c r="X39" s="163" t="n">
         <v>643.969071433097</v>
       </c>
       <c r="Y39" s="161" t="n">
-        <v>34.48356495677098</v>
+        <v>34.48356495677097</v>
       </c>
       <c r="Z39" s="162" t="n">
-        <v>40.53602049109927</v>
+        <v>40.53602049109926</v>
       </c>
       <c r="AA39" s="162" t="n">
         <v>45.8365565567824</v>
       </c>
       <c r="AB39" s="162" t="n">
-        <v>53.42238927713217</v>
+        <v>53.42238927713215</v>
       </c>
       <c r="AC39" s="163" t="n">
         <v>59.36782438609146</v>
@@ -4905,7 +4905,7 @@
         <v>20806955.9270134</v>
       </c>
       <c r="AG39" s="165" t="n">
-        <v>24477595.56591722</v>
+        <v>24477595.56591721</v>
       </c>
       <c r="AH39" s="166" t="n">
         <v>27510630.83557202</v>
@@ -4918,49 +4918,49 @@
         </is>
       </c>
       <c r="C40" s="155" t="n">
-        <v>3903.157151386098</v>
+        <v>3903.157151386096</v>
       </c>
       <c r="D40" s="156" t="n">
-        <v>4343.945887805073</v>
+        <v>4343.945887805071</v>
       </c>
       <c r="E40" s="156" t="n">
-        <v>4467.656743127438</v>
+        <v>4467.656743127435</v>
       </c>
       <c r="F40" s="156" t="n">
-        <v>4939.927426339694</v>
+        <v>4939.927426339693</v>
       </c>
       <c r="G40" s="157" t="n">
-        <v>5387.514444619563</v>
+        <v>5387.51444461956</v>
       </c>
       <c r="H40" s="155" t="n">
-        <v>3888.560102448786</v>
+        <v>3888.560102448784</v>
       </c>
       <c r="I40" s="156" t="n">
-        <v>4324.291469355593</v>
+        <v>4324.291469355591</v>
       </c>
       <c r="J40" s="156" t="n">
-        <v>4156.06141494582</v>
+        <v>4156.061414945817</v>
       </c>
       <c r="K40" s="156" t="n">
-        <v>4530.277702660615</v>
+        <v>4530.277702660614</v>
       </c>
       <c r="L40" s="157" t="n">
-        <v>4952.596524800789</v>
+        <v>4952.596524800787</v>
       </c>
       <c r="M40" s="158" t="n">
         <v>1947530.322897744</v>
       </c>
       <c r="N40" s="159" t="n">
-        <v>2310876.335607692</v>
+        <v>2310876.335607691</v>
       </c>
       <c r="O40" s="159" t="n">
-        <v>2486947.080863287</v>
+        <v>2486947.080863286</v>
       </c>
       <c r="P40" s="159" t="n">
-        <v>2908910.328771539</v>
+        <v>2908910.328771538</v>
       </c>
       <c r="Q40" s="160" t="n">
-        <v>3429598.299762172</v>
+        <v>3429598.299762171</v>
       </c>
       <c r="S40" s="32" t="inlineStr">
         <is>
@@ -4968,49 +4968,49 @@
         </is>
       </c>
       <c r="T40" s="155" t="n">
-        <v>3190.219615942628</v>
+        <v>3190.219615942627</v>
       </c>
       <c r="U40" s="156" t="n">
-        <v>3550.495366794986</v>
+        <v>3550.495366794985</v>
       </c>
       <c r="V40" s="156" t="n">
-        <v>3651.609614068965</v>
+        <v>3651.609614068962</v>
       </c>
       <c r="W40" s="156" t="n">
-        <v>4037.616925376766</v>
+        <v>4037.616925376765</v>
       </c>
       <c r="X40" s="157" t="n">
-        <v>4403.44920682888</v>
+        <v>4403.449206828878</v>
       </c>
       <c r="Y40" s="155" t="n">
-        <v>3180.461388882715</v>
+        <v>3180.461388882714</v>
       </c>
       <c r="Z40" s="156" t="n">
-        <v>3537.354368711184</v>
+        <v>3537.354368711183</v>
       </c>
       <c r="AA40" s="156" t="n">
-        <v>3440.76224389547</v>
+        <v>3440.762243895467</v>
       </c>
       <c r="AB40" s="156" t="n">
-        <v>3759.741362533297</v>
+        <v>3759.741362533296</v>
       </c>
       <c r="AC40" s="157" t="n">
-        <v>4108.553884095332</v>
+        <v>4108.55388409533</v>
       </c>
       <c r="AD40" s="158" t="n">
         <v>1947530.322897744</v>
       </c>
       <c r="AE40" s="159" t="n">
-        <v>2310876.335607692</v>
+        <v>2310876.335607691</v>
       </c>
       <c r="AF40" s="159" t="n">
-        <v>2486947.080863287</v>
+        <v>2486947.080863286</v>
       </c>
       <c r="AG40" s="159" t="n">
-        <v>2908910.328771539</v>
+        <v>2908910.328771538</v>
       </c>
       <c r="AH40" s="160" t="n">
-        <v>3429598.299762172</v>
+        <v>3429598.299762171</v>
       </c>
     </row>
     <row r="41" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -5020,22 +5020,22 @@
         </is>
       </c>
       <c r="C41" s="179" t="n">
-        <v>359.9889878884621</v>
+        <v>359.988987888462</v>
       </c>
       <c r="D41" s="180" t="n">
-        <v>404.6948761566286</v>
+        <v>404.6948761566285</v>
       </c>
       <c r="E41" s="180" t="n">
         <v>444.4653590489197</v>
       </c>
       <c r="F41" s="180" t="n">
-        <v>489.9208819966501</v>
+        <v>489.9208819966499</v>
       </c>
       <c r="G41" s="181" t="n">
         <v>531.7507818103559</v>
       </c>
       <c r="H41" s="179" t="n">
-        <v>34.03584100856929</v>
+        <v>34.03584100856928</v>
       </c>
       <c r="I41" s="180" t="n">
         <v>39.90820757769603</v>
@@ -5044,13 +5044,13 @@
         <v>44.77547517037821</v>
       </c>
       <c r="K41" s="180" t="n">
-        <v>52.10659419254768</v>
+        <v>52.10659419254767</v>
       </c>
       <c r="L41" s="181" t="n">
-        <v>58.16386265635764</v>
+        <v>58.16386265635763</v>
       </c>
       <c r="M41" s="182" t="n">
-        <v>16910003.40925008</v>
+        <v>16910003.40925007</v>
       </c>
       <c r="N41" s="183" t="n">
         <v>20385630.73916322</v>
@@ -5059,7 +5059,7 @@
         <v>23293903.00787669</v>
       </c>
       <c r="P41" s="183" t="n">
-        <v>27386505.89468876</v>
+        <v>27386505.89468875</v>
       </c>
       <c r="Q41" s="184" t="n">
         <v>30940229.13533419</v>
@@ -5070,37 +5070,37 @@
         </is>
       </c>
       <c r="T41" s="185" t="n">
-        <v>484.0185615432303</v>
+        <v>484.0185615432302</v>
       </c>
       <c r="U41" s="186" t="n">
-        <v>543.5889292745329</v>
+        <v>543.5889292745328</v>
       </c>
       <c r="V41" s="186" t="n">
         <v>596.1791883625164</v>
       </c>
       <c r="W41" s="186" t="n">
-        <v>656.3520526965517</v>
+        <v>656.3520526965515</v>
       </c>
       <c r="X41" s="187" t="n">
-        <v>711.2816345803682</v>
+        <v>711.2816345803681</v>
       </c>
       <c r="Y41" s="185" t="n">
-        <v>38.91705837834751</v>
+        <v>38.91705837834749</v>
       </c>
       <c r="Z41" s="186" t="n">
-        <v>45.65170903531457</v>
+        <v>45.65170903531456</v>
       </c>
       <c r="AA41" s="186" t="n">
         <v>51.23358401195281</v>
       </c>
       <c r="AB41" s="186" t="n">
-        <v>59.67033110976516</v>
+        <v>59.67033110976515</v>
       </c>
       <c r="AC41" s="187" t="n">
         <v>66.64882321318053</v>
       </c>
       <c r="AD41" s="188" t="n">
-        <v>16910003.40925008</v>
+        <v>16910003.40925007</v>
       </c>
       <c r="AE41" s="189" t="n">
         <v>20385630.73916322</v>
@@ -5109,7 +5109,7 @@
         <v>23293903.00787669</v>
       </c>
       <c r="AG41" s="189" t="n">
-        <v>27386505.89468876</v>
+        <v>27386505.89468875</v>
       </c>
       <c r="AH41" s="190" t="n">
         <v>30940229.13533419</v>
@@ -6334,49 +6334,49 @@
         </is>
       </c>
       <c r="C57" s="148" t="n">
-        <v>0.1601028446281169</v>
+        <v>0.1601028446281168</v>
       </c>
       <c r="D57" s="149" t="n">
-        <v>0.07635526788814721</v>
+        <v>0.07635526788814719</v>
       </c>
       <c r="E57" s="149" t="n">
-        <v>0.05837663786780951</v>
+        <v>0.05837663786780948</v>
       </c>
       <c r="F57" s="149" t="n">
-        <v>0.03994201092333402</v>
+        <v>0.03994201092333401</v>
       </c>
       <c r="G57" s="150" t="n">
-        <v>0.02373115240986779</v>
+        <v>0.02373115240986778</v>
       </c>
       <c r="H57" s="148" t="n">
-        <v>0.02415676513853763</v>
+        <v>0.02415676513853762</v>
       </c>
       <c r="I57" s="149" t="n">
         <v>0.01193424805774087</v>
       </c>
       <c r="J57" s="149" t="n">
-        <v>0.00923300059110487</v>
+        <v>0.009233000591104865</v>
       </c>
       <c r="K57" s="149" t="n">
-        <v>0.006599353115754897</v>
+        <v>0.006599353115754895</v>
       </c>
       <c r="L57" s="150" t="n">
-        <v>0.003982923134951569</v>
+        <v>0.003982923134951567</v>
       </c>
       <c r="M57" s="151" t="n">
-        <v>6211.110578893265</v>
+        <v>6211.110578893264</v>
       </c>
       <c r="N57" s="152" t="n">
-        <v>3155.098313709747</v>
+        <v>3155.098313709746</v>
       </c>
       <c r="O57" s="152" t="n">
-        <v>2487.073290022502</v>
+        <v>2487.0732900225</v>
       </c>
       <c r="P57" s="152" t="n">
-        <v>1799.842976985551</v>
+        <v>1799.84297698555</v>
       </c>
       <c r="Q57" s="153" t="n">
-        <v>1103.003879535713</v>
+        <v>1103.003879535712</v>
       </c>
       <c r="S57" s="21" t="inlineStr">
         <is>
@@ -6384,49 +6384,49 @@
         </is>
       </c>
       <c r="T57" s="148" t="n">
-        <v>0.2236269039141771</v>
+        <v>0.223626903914177</v>
       </c>
       <c r="U57" s="149" t="n">
-        <v>0.1066507731016621</v>
+        <v>0.106650773101662</v>
       </c>
       <c r="V57" s="149" t="n">
-        <v>0.08153875602660426</v>
+        <v>0.08153875602660422</v>
       </c>
       <c r="W57" s="149" t="n">
-        <v>0.05578981597509227</v>
+        <v>0.05578981597509225</v>
       </c>
       <c r="X57" s="150" t="n">
-        <v>0.0331469696997639</v>
+        <v>0.03314696969976389</v>
       </c>
       <c r="Y57" s="148" t="n">
-        <v>0.03054162049908171</v>
+        <v>0.03054162049908169</v>
       </c>
       <c r="Z57" s="149" t="n">
         <v>0.01509771232810036</v>
       </c>
       <c r="AA57" s="149" t="n">
-        <v>0.0116828663347586</v>
+        <v>0.01168286633475859</v>
       </c>
       <c r="AB57" s="149" t="n">
-        <v>0.008357007708401764</v>
+        <v>0.008357007708401762</v>
       </c>
       <c r="AC57" s="150" t="n">
-        <v>0.005045198630043801</v>
+        <v>0.005045198630043799</v>
       </c>
       <c r="AD57" s="151" t="n">
-        <v>6211.110578893265</v>
+        <v>6211.110578893264</v>
       </c>
       <c r="AE57" s="152" t="n">
-        <v>3155.098313709747</v>
+        <v>3155.098313709746</v>
       </c>
       <c r="AF57" s="152" t="n">
-        <v>2487.073290022502</v>
+        <v>2487.0732900225</v>
       </c>
       <c r="AG57" s="152" t="n">
-        <v>1799.842976985551</v>
+        <v>1799.84297698555</v>
       </c>
       <c r="AH57" s="153" t="n">
-        <v>1103.003879535713</v>
+        <v>1103.003879535712</v>
       </c>
     </row>
     <row r="58" ht="15" customHeight="1" thickBot="1">
@@ -6439,10 +6439,10 @@
         <v>0.2773194171680924</v>
       </c>
       <c r="D58" s="156" t="n">
-        <v>0.05609682008471067</v>
+        <v>0.05609682008471066</v>
       </c>
       <c r="E58" s="156" t="n">
-        <v>0.04119876279439152</v>
+        <v>0.04119876279439151</v>
       </c>
       <c r="F58" s="156" t="n">
         <v>0.02689540012736986</v>
@@ -6469,10 +6469,10 @@
         <v>2083.38692184318</v>
       </c>
       <c r="N58" s="159" t="n">
-        <v>467.6665174358655</v>
+        <v>467.6665174358654</v>
       </c>
       <c r="O58" s="159" t="n">
-        <v>372.8446500991478</v>
+        <v>372.8446500991477</v>
       </c>
       <c r="P58" s="159" t="n">
         <v>269.6227036357592</v>
@@ -6489,7 +6489,7 @@
         <v>0.3256643773508615</v>
       </c>
       <c r="U58" s="156" t="n">
-        <v>0.06587615166224484</v>
+        <v>0.06587615166224482</v>
       </c>
       <c r="V58" s="156" t="n">
         <v>0.04838092323311383</v>
@@ -6507,7 +6507,7 @@
         <v>0.002005835503441954</v>
       </c>
       <c r="AA58" s="156" t="n">
-        <v>0.001571649158099744</v>
+        <v>0.001571649158099743</v>
       </c>
       <c r="AB58" s="156" t="n">
         <v>0.00112832661943189</v>
@@ -6519,10 +6519,10 @@
         <v>2083.38692184318</v>
       </c>
       <c r="AE58" s="159" t="n">
-        <v>467.6665174358655</v>
+        <v>467.6665174358654</v>
       </c>
       <c r="AF58" s="159" t="n">
-        <v>372.8446500991478</v>
+        <v>372.8446500991477</v>
       </c>
       <c r="AG58" s="159" t="n">
         <v>269.6227036357592</v>
@@ -6541,43 +6541,43 @@
         <v>0.1791193689401478</v>
       </c>
       <c r="D59" s="162" t="n">
-        <v>0.07295420705949712</v>
+        <v>0.07295420705949709</v>
       </c>
       <c r="E59" s="162" t="n">
-        <v>0.05536702392937105</v>
+        <v>0.05536702392937103</v>
       </c>
       <c r="F59" s="162" t="n">
-        <v>0.03756772599649911</v>
+        <v>0.0375677259964991</v>
       </c>
       <c r="G59" s="163" t="n">
-        <v>0.02207603409869994</v>
+        <v>0.02207603409869993</v>
       </c>
       <c r="H59" s="161" t="n">
         <v>0.01683834956458635</v>
       </c>
       <c r="I59" s="162" t="n">
-        <v>0.00715327190409491</v>
+        <v>0.007153271904094908</v>
       </c>
       <c r="J59" s="162" t="n">
-        <v>0.00554521286145551</v>
+        <v>0.005545212861455508</v>
       </c>
       <c r="K59" s="162" t="n">
-        <v>0.003972030402015094</v>
+        <v>0.003972030402015093</v>
       </c>
       <c r="L59" s="163" t="n">
-        <v>0.002398838247032935</v>
+        <v>0.002398838247032934</v>
       </c>
       <c r="M59" s="164" t="n">
         <v>8294.497500736445</v>
       </c>
       <c r="N59" s="165" t="n">
-        <v>3622.764831145612</v>
+        <v>3622.764831145611</v>
       </c>
       <c r="O59" s="165" t="n">
-        <v>2859.917940121649</v>
+        <v>2859.917940121648</v>
       </c>
       <c r="P59" s="165" t="n">
-        <v>2069.46568062131</v>
+        <v>2069.465680621309</v>
       </c>
       <c r="Q59" s="166" t="n">
         <v>1264.848019633703</v>
@@ -6591,43 +6591,43 @@
         <v>0.2427294743053825</v>
       </c>
       <c r="U59" s="162" t="n">
-        <v>0.09875967397172969</v>
+        <v>0.09875967397172966</v>
       </c>
       <c r="V59" s="162" t="n">
-        <v>0.07485095031377897</v>
+        <v>0.07485095031377893</v>
       </c>
       <c r="W59" s="162" t="n">
-        <v>0.05072492323785447</v>
+        <v>0.05072492323785446</v>
       </c>
       <c r="X59" s="163" t="n">
-        <v>0.02977061791844373</v>
+        <v>0.02977061791844372</v>
       </c>
       <c r="Y59" s="161" t="n">
         <v>0.01927902960338238</v>
       </c>
       <c r="Z59" s="162" t="n">
-        <v>0.008193861922694241</v>
+        <v>0.008193861922694237</v>
       </c>
       <c r="AA59" s="162" t="n">
-        <v>0.006353769353998404</v>
+        <v>0.0063537693539984</v>
       </c>
       <c r="AB59" s="162" t="n">
-        <v>0.004555010258909451</v>
+        <v>0.00455501025890945</v>
       </c>
       <c r="AC59" s="163" t="n">
-        <v>0.002752745924558345</v>
+        <v>0.002752745924558344</v>
       </c>
       <c r="AD59" s="164" t="n">
         <v>8294.497500736445</v>
       </c>
       <c r="AE59" s="165" t="n">
-        <v>3622.764831145612</v>
+        <v>3622.764831145611</v>
       </c>
       <c r="AF59" s="165" t="n">
-        <v>2859.917940121649</v>
+        <v>2859.917940121648</v>
       </c>
       <c r="AG59" s="165" t="n">
-        <v>2069.46568062131</v>
+        <v>2069.465680621309</v>
       </c>
       <c r="AH59" s="166" t="n">
         <v>1264.848019633703</v>
@@ -6745,28 +6745,28 @@
         <v>0.1791547502109829</v>
       </c>
       <c r="D61" s="162" t="n">
-        <v>0.07268663652238708</v>
+        <v>0.07268663652238705</v>
       </c>
       <c r="E61" s="162" t="n">
-        <v>0.05515523280095686</v>
+        <v>0.05515523280095683</v>
       </c>
       <c r="F61" s="162" t="n">
         <v>0.03741508524221988</v>
       </c>
       <c r="G61" s="163" t="n">
-        <v>0.02197862720484592</v>
+        <v>0.02197862720484591</v>
       </c>
       <c r="H61" s="161" t="n">
         <v>0.01677551204748159</v>
       </c>
       <c r="I61" s="162" t="n">
-        <v>0.007099582225653703</v>
+        <v>0.0070995822256537</v>
       </c>
       <c r="J61" s="162" t="n">
-        <v>0.005503656700132835</v>
+        <v>0.005503656700132832</v>
       </c>
       <c r="K61" s="162" t="n">
-        <v>0.003942259315671832</v>
+        <v>0.003942259315671831</v>
       </c>
       <c r="L61" s="163" t="n">
         <v>0.002380859607585203</v>
@@ -6775,13 +6775,13 @@
         <v>8326.164300336659</v>
       </c>
       <c r="N61" s="165" t="n">
-        <v>3622.764831145612</v>
+        <v>3622.764831145611</v>
       </c>
       <c r="O61" s="165" t="n">
-        <v>2859.917940121649</v>
+        <v>2859.917940121648</v>
       </c>
       <c r="P61" s="165" t="n">
-        <v>2069.46568062131</v>
+        <v>2069.465680621309</v>
       </c>
       <c r="Q61" s="166" t="n">
         <v>1264.848019633703</v>
@@ -6795,43 +6795,43 @@
         <v>0.2425599319412705</v>
       </c>
       <c r="U61" s="162" t="n">
-        <v>0.09830828363330421</v>
+        <v>0.09830828363330418</v>
       </c>
       <c r="V61" s="162" t="n">
-        <v>0.07449462943836931</v>
+        <v>0.07449462943836928</v>
       </c>
       <c r="W61" s="162" t="n">
-        <v>0.05046876868101417</v>
+        <v>0.05046876868101416</v>
       </c>
       <c r="X61" s="163" t="n">
-        <v>0.02960757278071234</v>
+        <v>0.02960757278071233</v>
       </c>
       <c r="Y61" s="161" t="n">
         <v>0.01918906225156674</v>
       </c>
       <c r="Z61" s="162" t="n">
-        <v>0.008124728344904349</v>
+        <v>0.008124728344904348</v>
       </c>
       <c r="AA61" s="162" t="n">
-        <v>0.006300238769667971</v>
+        <v>0.006300238769667968</v>
       </c>
       <c r="AB61" s="162" t="n">
-        <v>0.004516611972286836</v>
+        <v>0.004516611972286835</v>
       </c>
       <c r="AC61" s="163" t="n">
-        <v>0.00272953664906928</v>
+        <v>0.002729536649069279</v>
       </c>
       <c r="AD61" s="164" t="n">
         <v>8326.164300336659</v>
       </c>
       <c r="AE61" s="165" t="n">
-        <v>3622.764831145612</v>
+        <v>3622.764831145611</v>
       </c>
       <c r="AF61" s="165" t="n">
-        <v>2859.917940121649</v>
+        <v>2859.917940121648</v>
       </c>
       <c r="AG61" s="165" t="n">
-        <v>2069.46568062131</v>
+        <v>2069.465680621309</v>
       </c>
       <c r="AH61" s="166" t="n">
         <v>1264.848019633703</v>
@@ -6949,43 +6949,43 @@
         <v>0.1772517359654491</v>
       </c>
       <c r="D63" s="180" t="n">
-        <v>0.07191900920036204</v>
+        <v>0.07191900920036201</v>
       </c>
       <c r="E63" s="180" t="n">
-        <v>0.0545694061521931</v>
+        <v>0.05456940615219307</v>
       </c>
       <c r="F63" s="180" t="n">
         <v>0.03702094949280905</v>
       </c>
       <c r="G63" s="181" t="n">
-        <v>0.02173816878891183</v>
+        <v>0.02173816878891182</v>
       </c>
       <c r="H63" s="179" t="n">
         <v>0.01675860125388654</v>
       </c>
       <c r="I63" s="180" t="n">
-        <v>0.00709215489755656</v>
+        <v>0.007092154897556558</v>
       </c>
       <c r="J63" s="180" t="n">
-        <v>0.005497326260607136</v>
+        <v>0.005497326260607133</v>
       </c>
       <c r="K63" s="180" t="n">
-        <v>0.003937443090776024</v>
+        <v>0.003937443090776023</v>
       </c>
       <c r="L63" s="181" t="n">
-        <v>0.002377760234849859</v>
+        <v>0.002377760234849858</v>
       </c>
       <c r="M63" s="182" t="n">
         <v>8326.164300336659</v>
       </c>
       <c r="N63" s="183" t="n">
-        <v>3622.764831145612</v>
+        <v>3622.764831145611</v>
       </c>
       <c r="O63" s="183" t="n">
-        <v>2859.917940121649</v>
+        <v>2859.917940121648</v>
       </c>
       <c r="P63" s="183" t="n">
-        <v>2069.46568062131</v>
+        <v>2069.465680621309</v>
       </c>
       <c r="Q63" s="184" t="n">
         <v>1264.848019633703</v>
@@ -6999,43 +6999,43 @@
         <v>0.2383215408234071</v>
       </c>
       <c r="U63" s="186" t="n">
-        <v>0.09660210570736119</v>
+        <v>0.09660210570736115</v>
       </c>
       <c r="V63" s="186" t="n">
-        <v>0.0731961301525374</v>
+        <v>0.07319613015253736</v>
       </c>
       <c r="W63" s="186" t="n">
-        <v>0.04959734741934665</v>
+        <v>0.04959734741934663</v>
       </c>
       <c r="X63" s="187" t="n">
-        <v>0.0290774565038167</v>
+        <v>0.02907745650381669</v>
       </c>
       <c r="Y63" s="185" t="n">
         <v>0.01916201991814292</v>
       </c>
       <c r="Z63" s="186" t="n">
-        <v>0.008112842231420633</v>
+        <v>0.00811284223142063</v>
       </c>
       <c r="AA63" s="186" t="n">
-        <v>0.006290223068369754</v>
+        <v>0.006290223068369751</v>
       </c>
       <c r="AB63" s="186" t="n">
         <v>0.004508998075834035</v>
       </c>
       <c r="AC63" s="187" t="n">
-        <v>0.002724628563136129</v>
+        <v>0.002724628563136128</v>
       </c>
       <c r="AD63" s="188" t="n">
         <v>8326.164300336659</v>
       </c>
       <c r="AE63" s="189" t="n">
-        <v>3622.764831145612</v>
+        <v>3622.764831145611</v>
       </c>
       <c r="AF63" s="189" t="n">
-        <v>2859.917940121649</v>
+        <v>2859.917940121648</v>
       </c>
       <c r="AG63" s="189" t="n">
-        <v>2069.46568062131</v>
+        <v>2069.465680621309</v>
       </c>
       <c r="AH63" s="190" t="n">
         <v>1264.848019633703</v>
@@ -7297,49 +7297,49 @@
         </is>
       </c>
       <c r="C68" s="148" t="n">
-        <v>0.6338698040143974</v>
+        <v>0.633869804014397</v>
       </c>
       <c r="D68" s="149" t="n">
-        <v>0.5926074485313442</v>
+        <v>0.5926074485313441</v>
       </c>
       <c r="E68" s="149" t="n">
-        <v>0.680952991578758</v>
+        <v>0.6809529915787577</v>
       </c>
       <c r="F68" s="149" t="n">
-        <v>0.7598414310593248</v>
+        <v>0.7598414310593246</v>
       </c>
       <c r="G68" s="150" t="n">
-        <v>0.7920665016711131</v>
+        <v>0.7920665016711128</v>
       </c>
       <c r="H68" s="148" t="n">
-        <v>0.09564004949164769</v>
+        <v>0.0956400494916476</v>
       </c>
       <c r="I68" s="149" t="n">
-        <v>0.09262392087993471</v>
+        <v>0.09262392087993469</v>
       </c>
       <c r="J68" s="149" t="n">
-        <v>0.1077012929041647</v>
+        <v>0.1077012929041646</v>
       </c>
       <c r="K68" s="149" t="n">
-        <v>0.125543551754716</v>
+        <v>0.1255435517547159</v>
       </c>
       <c r="L68" s="150" t="n">
-        <v>0.1329366538733383</v>
+        <v>0.1329366538733382</v>
       </c>
       <c r="M68" s="151" t="n">
-        <v>24590.66517212532</v>
+        <v>24590.6651721253</v>
       </c>
       <c r="N68" s="152" t="n">
-        <v>24487.30537219846</v>
+        <v>24487.30537219845</v>
       </c>
       <c r="O68" s="152" t="n">
-        <v>29011.26304929482</v>
+        <v>29011.2630492948</v>
       </c>
       <c r="P68" s="152" t="n">
-        <v>34239.51953595382</v>
+        <v>34239.51953595381</v>
       </c>
       <c r="Q68" s="153" t="n">
-        <v>36814.58064506969</v>
+        <v>36814.58064506968</v>
       </c>
       <c r="S68" s="21" t="inlineStr">
         <is>
@@ -7347,13 +7347,13 @@
         </is>
       </c>
       <c r="T68" s="148" t="n">
-        <v>0.8853705384540813</v>
+        <v>0.8853705384540806</v>
       </c>
       <c r="U68" s="149" t="n">
-        <v>0.8277365043660893</v>
+        <v>0.8277365043660891</v>
       </c>
       <c r="V68" s="149" t="n">
-        <v>0.9511349381178419</v>
+        <v>0.9511349381178413</v>
       </c>
       <c r="W68" s="149" t="n">
         <v>1.061323970153078</v>
@@ -7362,13 +7362,13 @@
         <v>1.106334992824592</v>
       </c>
       <c r="Y68" s="148" t="n">
-        <v>0.120918594825736</v>
+        <v>0.1209185948257359</v>
       </c>
       <c r="Z68" s="149" t="n">
         <v>0.1171761559991153</v>
       </c>
       <c r="AA68" s="149" t="n">
-        <v>0.136278536610542</v>
+        <v>0.1362785366105419</v>
       </c>
       <c r="AB68" s="149" t="n">
         <v>0.1589804957170083</v>
@@ -7377,19 +7377,19 @@
         <v>0.1683918572564992</v>
       </c>
       <c r="AD68" s="151" t="n">
-        <v>24590.66517212532</v>
+        <v>24590.6651721253</v>
       </c>
       <c r="AE68" s="152" t="n">
-        <v>24487.30537219846</v>
+        <v>24487.30537219845</v>
       </c>
       <c r="AF68" s="152" t="n">
-        <v>29011.26304929482</v>
+        <v>29011.2630492948</v>
       </c>
       <c r="AG68" s="152" t="n">
-        <v>34239.51953595382</v>
+        <v>34239.51953595381</v>
       </c>
       <c r="AH68" s="153" t="n">
-        <v>36814.58064506969</v>
+        <v>36814.58064506968</v>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1" thickBot="1">
@@ -7420,13 +7420,13 @@
         <v>0.03679308275083937</v>
       </c>
       <c r="J69" s="156" t="n">
-        <v>0.04498423356920219</v>
+        <v>0.04498423356920217</v>
       </c>
       <c r="K69" s="156" t="n">
         <v>0.05442633610138456</v>
       </c>
       <c r="L69" s="157" t="n">
-        <v>0.06395932865333599</v>
+        <v>0.06395932865333601</v>
       </c>
       <c r="M69" s="158" t="n">
         <v>10317.50320865423</v>
@@ -7455,7 +7455,7 @@
         <v>1.254609019318191</v>
       </c>
       <c r="V69" s="156" t="n">
-        <v>1.438161670737746</v>
+        <v>1.438161670737745</v>
       </c>
       <c r="W69" s="156" t="n">
         <v>1.582928012227113</v>
@@ -7470,7 +7470,7 @@
         <v>0.03820106746352655</v>
       </c>
       <c r="AA69" s="156" t="n">
-        <v>0.04671852928757815</v>
+        <v>0.04671852928757812</v>
       </c>
       <c r="AB69" s="156" t="n">
         <v>0.0565494013555404</v>
@@ -7501,49 +7501,49 @@
         </is>
       </c>
       <c r="C70" s="161" t="n">
-        <v>0.7538406142947771</v>
+        <v>0.7538406142947767</v>
       </c>
       <c r="D70" s="162" t="n">
         <v>0.6724788260503037</v>
       </c>
       <c r="E70" s="162" t="n">
-        <v>0.7762131358816733</v>
+        <v>0.7762131358816728</v>
       </c>
       <c r="F70" s="162" t="n">
-        <v>0.8668667883910289</v>
+        <v>0.8668667883910287</v>
       </c>
       <c r="G70" s="163" t="n">
-        <v>0.922003965551483</v>
+        <v>0.9220039655514829</v>
       </c>
       <c r="H70" s="161" t="n">
-        <v>0.07086576875848326</v>
+        <v>0.07086576875848322</v>
       </c>
       <c r="I70" s="162" t="n">
         <v>0.06593758038602585</v>
       </c>
       <c r="J70" s="162" t="n">
-        <v>0.07774062535513028</v>
+        <v>0.07774062535513024</v>
       </c>
       <c r="K70" s="162" t="n">
-        <v>0.09165370398802476</v>
+        <v>0.09165370398802473</v>
       </c>
       <c r="L70" s="163" t="n">
         <v>0.1001873056814667</v>
       </c>
       <c r="M70" s="164" t="n">
-        <v>34908.16838077955</v>
+        <v>34908.16838077953</v>
       </c>
       <c r="N70" s="165" t="n">
         <v>33393.99794611271</v>
       </c>
       <c r="O70" s="165" t="n">
-        <v>40094.36872564984</v>
+        <v>40094.36872564982</v>
       </c>
       <c r="P70" s="165" t="n">
-        <v>47752.45295424125</v>
+        <v>47752.45295424123</v>
       </c>
       <c r="Q70" s="166" t="n">
-        <v>52826.28594920008</v>
+        <v>52826.28594920007</v>
       </c>
       <c r="S70" s="42" t="inlineStr">
         <is>
@@ -7551,13 +7551,13 @@
         </is>
       </c>
       <c r="T70" s="161" t="n">
-        <v>1.021549691138985</v>
+        <v>1.021549691138984</v>
       </c>
       <c r="U70" s="162" t="n">
         <v>0.9103490023468609</v>
       </c>
       <c r="V70" s="162" t="n">
-        <v>1.049366332943908</v>
+        <v>1.049366332943907</v>
       </c>
       <c r="W70" s="162" t="n">
         <v>1.170466141673788</v>
@@ -7566,13 +7566,13 @@
         <v>1.243367701599066</v>
       </c>
       <c r="Y70" s="161" t="n">
-        <v>0.08113759893871235</v>
+        <v>0.08113759893871229</v>
       </c>
       <c r="Z70" s="162" t="n">
         <v>0.07552955297146766</v>
       </c>
       <c r="AA70" s="162" t="n">
-        <v>0.0890761121859706</v>
+        <v>0.08907611218597054</v>
       </c>
       <c r="AB70" s="162" t="n">
         <v>0.1051058324530207</v>
@@ -7581,19 +7581,19 @@
         <v>0.1149682342059774</v>
       </c>
       <c r="AD70" s="164" t="n">
-        <v>34908.16838077955</v>
+        <v>34908.16838077953</v>
       </c>
       <c r="AE70" s="165" t="n">
         <v>33393.99794611271</v>
       </c>
       <c r="AF70" s="165" t="n">
-        <v>40094.36872564984</v>
+        <v>40094.36872564982</v>
       </c>
       <c r="AG70" s="165" t="n">
-        <v>47752.45295424125</v>
+        <v>47752.45295424123</v>
       </c>
       <c r="AH70" s="166" t="n">
-        <v>52826.28594920008</v>
+        <v>52826.28594920007</v>
       </c>
     </row>
     <row r="71" ht="15" customHeight="1" thickBot="1">
@@ -7609,7 +7609,7 @@
         <v>3.693837158925251</v>
       </c>
       <c r="E71" s="156" t="n">
-        <v>4.428624384034901</v>
+        <v>4.428624384034902</v>
       </c>
       <c r="F71" s="156" t="n">
         <v>4.864024318298082</v>
@@ -7624,7 +7624,7 @@
         <v>0.1763022463350242</v>
       </c>
       <c r="J71" s="156" t="n">
-        <v>0.2255655873251499</v>
+        <v>0.22556558732515</v>
       </c>
       <c r="K71" s="156" t="n">
         <v>0.2778226593323567</v>
@@ -7639,7 +7639,7 @@
         <v>675.2292778471705</v>
       </c>
       <c r="O71" s="159" t="n">
-        <v>878.3999070977121</v>
+        <v>878.3999070977123</v>
       </c>
       <c r="P71" s="159" t="n">
         <v>1093.107371254539</v>
@@ -7659,7 +7659,7 @@
         <v>4.008931393751021</v>
       </c>
       <c r="V71" s="156" t="n">
-        <v>4.806397943501782</v>
+        <v>4.806397943501783</v>
       </c>
       <c r="W71" s="156" t="n">
         <v>5.27893866205708</v>
@@ -7674,7 +7674,7 @@
         <v>0.1794814540004451</v>
       </c>
       <c r="AA71" s="156" t="n">
-        <v>0.2296810577273997</v>
+        <v>0.2296810577273998</v>
       </c>
       <c r="AB71" s="156" t="n">
         <v>0.2830055086747525</v>
@@ -7689,7 +7689,7 @@
         <v>675.2292778471705</v>
       </c>
       <c r="AF71" s="159" t="n">
-        <v>878.3999070977121</v>
+        <v>878.3999070977123</v>
       </c>
       <c r="AG71" s="159" t="n">
         <v>1093.107371254539</v>
@@ -7705,46 +7705,46 @@
         </is>
       </c>
       <c r="C72" s="161" t="n">
-        <v>0.7620213623938424</v>
+        <v>0.762021362393842</v>
       </c>
       <c r="D72" s="162" t="n">
         <v>0.6835601125794</v>
       </c>
       <c r="E72" s="162" t="n">
-        <v>0.7901844177888576</v>
+        <v>0.7901844177888572</v>
       </c>
       <c r="F72" s="162" t="n">
-        <v>0.8831075675213591</v>
+        <v>0.8831075675213589</v>
       </c>
       <c r="G72" s="163" t="n">
-        <v>0.9413165709678332</v>
+        <v>0.9413165709678331</v>
       </c>
       <c r="H72" s="161" t="n">
-        <v>0.07135338878942309</v>
+        <v>0.07135338878942303</v>
       </c>
       <c r="I72" s="162" t="n">
         <v>0.06676593466998378</v>
       </c>
       <c r="J72" s="162" t="n">
-        <v>0.07884843458096621</v>
+        <v>0.07884843458096617</v>
       </c>
       <c r="K72" s="162" t="n">
-        <v>0.09304907398347574</v>
+        <v>0.09304907398347571</v>
       </c>
       <c r="L72" s="163" t="n">
         <v>0.1019691803714561</v>
       </c>
       <c r="M72" s="164" t="n">
-        <v>35414.71859487741</v>
+        <v>35414.71859487739</v>
       </c>
       <c r="N72" s="165" t="n">
         <v>34069.22722395988</v>
       </c>
       <c r="O72" s="165" t="n">
-        <v>40972.76863274755</v>
+        <v>40972.76863274753</v>
       </c>
       <c r="P72" s="165" t="n">
-        <v>48845.56032549579</v>
+        <v>48845.56032549578</v>
       </c>
       <c r="Q72" s="166" t="n">
         <v>54171.82745492583</v>
@@ -7755,7 +7755,7 @@
         </is>
       </c>
       <c r="T72" s="161" t="n">
-        <v>1.031710571907088</v>
+        <v>1.031710571907087</v>
       </c>
       <c r="U72" s="162" t="n">
         <v>0.9245113633394209</v>
@@ -7770,31 +7770,31 @@
         <v>1.268054579790852</v>
       </c>
       <c r="Y72" s="161" t="n">
-        <v>0.08161924449549271</v>
+        <v>0.08161924449549265</v>
       </c>
       <c r="Z72" s="162" t="n">
         <v>0.07640662008633925</v>
       </c>
       <c r="AA72" s="162" t="n">
-        <v>0.09026071056769262</v>
+        <v>0.09026071056769257</v>
       </c>
       <c r="AB72" s="162" t="n">
         <v>0.1066055091539175</v>
       </c>
       <c r="AC72" s="163" t="n">
-        <v>0.1169025733448186</v>
+        <v>0.1169025733448185</v>
       </c>
       <c r="AD72" s="164" t="n">
-        <v>35414.71859487741</v>
+        <v>35414.71859487739</v>
       </c>
       <c r="AE72" s="165" t="n">
         <v>34069.22722395988</v>
       </c>
       <c r="AF72" s="165" t="n">
-        <v>40972.76863274755</v>
+        <v>40972.76863274753</v>
       </c>
       <c r="AG72" s="165" t="n">
-        <v>48845.56032549579</v>
+        <v>48845.56032549578</v>
       </c>
       <c r="AH72" s="166" t="n">
         <v>54171.82745492583</v>
@@ -7807,19 +7807,19 @@
         </is>
       </c>
       <c r="C73" s="155" t="n">
-        <v>16.27687319072329</v>
+        <v>16.27687319072328</v>
       </c>
       <c r="D73" s="156" t="n">
         <v>25.75633018503019</v>
       </c>
       <c r="E73" s="156" t="n">
-        <v>39.11906585717956</v>
+        <v>39.11906585717954</v>
       </c>
       <c r="F73" s="156" t="n">
-        <v>56.79460845809642</v>
+        <v>56.7946084580964</v>
       </c>
       <c r="G73" s="157" t="n">
-        <v>77.39076478310314</v>
+        <v>77.39076478310311</v>
       </c>
       <c r="H73" s="155" t="n">
         <v>16.21600084936059</v>
@@ -7828,28 +7828,28 @@
         <v>25.63979427407405</v>
       </c>
       <c r="J73" s="156" t="n">
-        <v>36.3907187918691</v>
+        <v>36.39071879186908</v>
       </c>
       <c r="K73" s="156" t="n">
-        <v>52.08484378882883</v>
+        <v>52.08484378882881</v>
       </c>
       <c r="L73" s="157" t="n">
-        <v>71.14323992193721</v>
+        <v>71.14323992193719</v>
       </c>
       <c r="M73" s="158" t="n">
-        <v>8121.5546470215</v>
+        <v>8121.554647021498</v>
       </c>
       <c r="N73" s="159" t="n">
         <v>13701.75767699508</v>
       </c>
       <c r="O73" s="159" t="n">
-        <v>21775.85527117035</v>
+        <v>21775.85527117034</v>
       </c>
       <c r="P73" s="159" t="n">
-        <v>33443.8968235424</v>
+        <v>33443.89682354239</v>
       </c>
       <c r="Q73" s="160" t="n">
-        <v>49265.61924720133</v>
+        <v>49265.61924720132</v>
       </c>
       <c r="S73" s="32" t="inlineStr">
         <is>
@@ -7857,49 +7857,49 @@
         </is>
       </c>
       <c r="T73" s="155" t="n">
-        <v>13.30379437087634</v>
+        <v>13.30379437087633</v>
       </c>
       <c r="U73" s="156" t="n">
         <v>21.05176568711786</v>
       </c>
       <c r="V73" s="156" t="n">
-        <v>31.9737090807648</v>
+        <v>31.97370908076478</v>
       </c>
       <c r="W73" s="156" t="n">
-        <v>46.42069661951907</v>
+        <v>46.42069661951905</v>
       </c>
       <c r="X73" s="157" t="n">
-        <v>63.25482841913761</v>
+        <v>63.2548284191376</v>
       </c>
       <c r="Y73" s="155" t="n">
-        <v>13.26310079430229</v>
+        <v>13.26310079430228</v>
       </c>
       <c r="Z73" s="156" t="n">
         <v>20.97384945741586</v>
       </c>
       <c r="AA73" s="156" t="n">
-        <v>30.12751707590271</v>
+        <v>30.12751707590269</v>
       </c>
       <c r="AB73" s="156" t="n">
-        <v>43.22594648865292</v>
+        <v>43.22594648865291</v>
       </c>
       <c r="AC73" s="157" t="n">
-        <v>59.01870528816365</v>
+        <v>59.01870528816364</v>
       </c>
       <c r="AD73" s="158" t="n">
-        <v>8121.5546470215</v>
+        <v>8121.554647021498</v>
       </c>
       <c r="AE73" s="159" t="n">
         <v>13701.75767699508</v>
       </c>
       <c r="AF73" s="159" t="n">
-        <v>21775.85527117035</v>
+        <v>21775.85527117034</v>
       </c>
       <c r="AG73" s="159" t="n">
-        <v>33443.8968235424</v>
+        <v>33443.89682354239</v>
       </c>
       <c r="AH73" s="160" t="n">
-        <v>49265.61924720133</v>
+        <v>49265.61924720132</v>
       </c>
     </row>
     <row r="74" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -7909,22 +7909,22 @@
         </is>
       </c>
       <c r="C74" s="179" t="n">
-        <v>0.926822932052961</v>
+        <v>0.9268229320529605</v>
       </c>
       <c r="D74" s="180" t="n">
         <v>0.9483480332659893</v>
       </c>
       <c r="E74" s="180" t="n">
-        <v>1.197291396115533</v>
+        <v>1.197291396115532</v>
       </c>
       <c r="F74" s="180" t="n">
         <v>1.472087150529887</v>
       </c>
       <c r="G74" s="181" t="n">
-        <v>1.777716089681734</v>
+        <v>1.777716089681733</v>
       </c>
       <c r="H74" s="179" t="n">
-        <v>0.0876282303619367</v>
+        <v>0.08762823036193665</v>
       </c>
       <c r="I74" s="180" t="n">
         <v>0.09351951901864715</v>
@@ -7936,22 +7936,22 @@
         <v>0.1565670102815686</v>
       </c>
       <c r="L74" s="181" t="n">
-        <v>0.1944498024623907</v>
+        <v>0.1944498024623906</v>
       </c>
       <c r="M74" s="182" t="n">
-        <v>43536.27324189891</v>
+        <v>43536.27324189889</v>
       </c>
       <c r="N74" s="183" t="n">
         <v>47770.98490095495</v>
       </c>
       <c r="O74" s="183" t="n">
-        <v>62748.6239039179</v>
+        <v>62748.62390391787</v>
       </c>
       <c r="P74" s="183" t="n">
-        <v>82289.45714903818</v>
+        <v>82289.45714903816</v>
       </c>
       <c r="Q74" s="184" t="n">
-        <v>103437.4467021272</v>
+        <v>103437.4467021271</v>
       </c>
       <c r="S74" s="51" t="inlineStr">
         <is>
@@ -7959,19 +7959,19 @@
         </is>
       </c>
       <c r="T74" s="185" t="n">
-        <v>1.246147847490674</v>
+        <v>1.246147847490673</v>
       </c>
       <c r="U74" s="186" t="n">
         <v>1.273827573203942</v>
       </c>
       <c r="V74" s="186" t="n">
-        <v>1.605974904989207</v>
+        <v>1.605974904989206</v>
       </c>
       <c r="W74" s="186" t="n">
         <v>1.972170320768478</v>
       </c>
       <c r="X74" s="187" t="n">
-        <v>2.377912453243183</v>
+        <v>2.377912453243182</v>
       </c>
       <c r="Y74" s="185" t="n">
         <v>0.1001953486540312</v>
@@ -7980,7 +7980,7 @@
         <v>0.1069786425022981</v>
       </c>
       <c r="AA74" s="186" t="n">
-        <v>0.1380119464449015</v>
+        <v>0.1380119464449014</v>
       </c>
       <c r="AB74" s="186" t="n">
         <v>0.179294108339619</v>
@@ -7989,19 +7989,19 @@
         <v>0.2228161940468575</v>
       </c>
       <c r="AD74" s="188" t="n">
-        <v>43536.27324189891</v>
+        <v>43536.27324189889</v>
       </c>
       <c r="AE74" s="189" t="n">
         <v>47770.98490095495</v>
       </c>
       <c r="AF74" s="189" t="n">
-        <v>62748.6239039179</v>
+        <v>62748.62390391787</v>
       </c>
       <c r="AG74" s="189" t="n">
-        <v>82289.45714903818</v>
+        <v>82289.45714903816</v>
       </c>
       <c r="AH74" s="190" t="n">
-        <v>103437.4467021272</v>
+        <v>103437.4467021271</v>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1" thickBot="1"/>
@@ -8260,7 +8260,7 @@
         </is>
       </c>
       <c r="C79" s="148" t="n">
-        <v>253.2437750495938</v>
+        <v>253.2437750495937</v>
       </c>
       <c r="D79" s="149" t="n">
         <v>284.9745748049518</v>
@@ -8269,28 +8269,28 @@
         <v>314.7381730030972</v>
       </c>
       <c r="F79" s="149" t="n">
-        <v>347.7581392889213</v>
+        <v>347.7581392889212</v>
       </c>
       <c r="G79" s="150" t="n">
         <v>375.5416178571006</v>
       </c>
       <c r="H79" s="148" t="n">
-        <v>38.21012931331355</v>
+        <v>38.21012931331354</v>
       </c>
       <c r="I79" s="149" t="n">
-        <v>44.54122629565765</v>
+        <v>44.54122629565764</v>
       </c>
       <c r="J79" s="149" t="n">
-        <v>49.7798065034386</v>
+        <v>49.77980650343859</v>
       </c>
       <c r="K79" s="149" t="n">
-        <v>57.45776707263247</v>
+        <v>57.45776707263246</v>
       </c>
       <c r="L79" s="150" t="n">
-        <v>63.02910925127383</v>
+        <v>63.02910925127382</v>
       </c>
       <c r="M79" s="151" t="n">
-        <v>9824466.853808576</v>
+        <v>9824466.853808573</v>
       </c>
       <c r="N79" s="152" t="n">
         <v>11775517.59407589</v>
@@ -8310,37 +8310,37 @@
         </is>
       </c>
       <c r="T79" s="148" t="n">
-        <v>353.7233924945104</v>
+        <v>353.7233924945103</v>
       </c>
       <c r="U79" s="149" t="n">
-        <v>398.0440322963424</v>
+        <v>398.0440322963423</v>
       </c>
       <c r="V79" s="149" t="n">
-        <v>439.6169433202353</v>
+        <v>439.6169433202352</v>
       </c>
       <c r="W79" s="149" t="n">
-        <v>485.7382526886045</v>
+        <v>485.7382526886044</v>
       </c>
       <c r="X79" s="150" t="n">
-        <v>524.5453913537517</v>
+        <v>524.5453913537516</v>
       </c>
       <c r="Y79" s="148" t="n">
-        <v>48.30941816983307</v>
+        <v>48.30941816983306</v>
       </c>
       <c r="Z79" s="149" t="n">
         <v>56.34796747135452</v>
       </c>
       <c r="AA79" s="149" t="n">
-        <v>62.98827990004776</v>
+        <v>62.98827990004775</v>
       </c>
       <c r="AB79" s="149" t="n">
-        <v>72.76091973123879</v>
+        <v>72.76091973123877</v>
       </c>
       <c r="AC79" s="150" t="n">
-        <v>79.83944577209986</v>
+        <v>79.83944577209984</v>
       </c>
       <c r="AD79" s="151" t="n">
-        <v>9824466.853808576</v>
+        <v>9824466.853808573</v>
       </c>
       <c r="AE79" s="152" t="n">
         <v>11775517.59407589</v>
@@ -8371,7 +8371,7 @@
         <v>799.0972238838542</v>
       </c>
       <c r="F80" s="156" t="n">
-        <v>858.2878462863857</v>
+        <v>858.2878462863856</v>
       </c>
       <c r="G80" s="157" t="n">
         <v>906.8952143099908</v>
@@ -8386,7 +8386,7 @@
         <v>29.35230521448854</v>
       </c>
       <c r="K80" s="156" t="n">
-        <v>34.65539670700931</v>
+        <v>34.6553967070093</v>
       </c>
       <c r="L80" s="157" t="n">
         <v>39.1820288923225</v>
@@ -8401,7 +8401,7 @@
         <v>7231749.320266848</v>
       </c>
       <c r="P80" s="159" t="n">
-        <v>8604218.138325889</v>
+        <v>8604218.138325887</v>
       </c>
       <c r="Q80" s="160" t="n">
         <v>9808906.895226892</v>
@@ -8421,7 +8421,7 @@
         <v>938.4034573431936</v>
       </c>
       <c r="W80" s="156" t="n">
-        <v>1007.912752388504</v>
+        <v>1007.912752388503</v>
       </c>
       <c r="X80" s="157" t="n">
         <v>1064.99381942564</v>
@@ -8436,7 +8436,7 @@
         <v>30.4839367488936</v>
       </c>
       <c r="AB80" s="156" t="n">
-        <v>36.00723616356547</v>
+        <v>36.00723616356546</v>
       </c>
       <c r="AC80" s="157" t="n">
         <v>40.72426922342281</v>
@@ -8451,7 +8451,7 @@
         <v>7231749.320266848</v>
       </c>
       <c r="AG80" s="159" t="n">
-        <v>8604218.138325889</v>
+        <v>8604218.138325887</v>
       </c>
       <c r="AH80" s="160" t="n">
         <v>9808906.895226892</v>
@@ -8470,10 +8470,10 @@
         <v>361.0954657906885</v>
       </c>
       <c r="E81" s="162" t="n">
-        <v>399.5992949119023</v>
+        <v>399.5992949119022</v>
       </c>
       <c r="F81" s="162" t="n">
-        <v>440.6667886678457</v>
+        <v>440.6667886678456</v>
       </c>
       <c r="G81" s="163" t="n">
         <v>475.8482935911645</v>
@@ -8485,13 +8485,13 @@
         <v>35.40596429250535</v>
       </c>
       <c r="J81" s="162" t="n">
-        <v>40.02135192241324</v>
+        <v>40.02135192241322</v>
       </c>
       <c r="K81" s="162" t="n">
-        <v>46.59163777733462</v>
+        <v>46.5916377773346</v>
       </c>
       <c r="L81" s="163" t="n">
-        <v>51.70689089119792</v>
+        <v>51.70689089119791</v>
       </c>
       <c r="M81" s="164" t="n">
         <v>14858852.13710955</v>
@@ -8503,10 +8503,10 @@
         <v>20640827.5408906</v>
       </c>
       <c r="P81" s="165" t="n">
-        <v>24274687.15627593</v>
+        <v>24274687.15627592</v>
       </c>
       <c r="Q81" s="166" t="n">
-        <v>27263763.45968346</v>
+        <v>27263763.45968345</v>
       </c>
       <c r="S81" s="42" t="inlineStr">
         <is>
@@ -8520,28 +8520,28 @@
         <v>488.8226726263329</v>
       </c>
       <c r="V81" s="162" t="n">
-        <v>540.2202402467414</v>
+        <v>540.2202402467412</v>
       </c>
       <c r="W81" s="162" t="n">
-        <v>594.9997886678406</v>
+        <v>594.9997886678404</v>
       </c>
       <c r="X81" s="163" t="n">
-        <v>641.7048312350744</v>
+        <v>641.7048312350743</v>
       </c>
       <c r="Y81" s="161" t="n">
-        <v>34.53666122609383</v>
+        <v>34.53666122609382</v>
       </c>
       <c r="Z81" s="162" t="n">
         <v>40.55648751259634</v>
       </c>
       <c r="AA81" s="162" t="n">
-        <v>45.85693023936851</v>
+        <v>45.85693023936849</v>
       </c>
       <c r="AB81" s="162" t="n">
-        <v>53.42995057325995</v>
+        <v>53.42995057325994</v>
       </c>
       <c r="AC81" s="163" t="n">
-        <v>59.33536091830282</v>
+        <v>59.33536091830281</v>
       </c>
       <c r="AD81" s="164" t="n">
         <v>14858852.13710955</v>
@@ -8553,10 +8553,10 @@
         <v>20640827.5408906</v>
       </c>
       <c r="AG81" s="165" t="n">
-        <v>24274687.15627593</v>
+        <v>24274687.15627592</v>
       </c>
       <c r="AH81" s="166" t="n">
-        <v>27263763.45968346</v>
+        <v>27263763.45968345</v>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1" thickBot="1">
@@ -8668,49 +8668,49 @@
         </is>
       </c>
       <c r="C83" s="161" t="n">
-        <v>322.8899188506769</v>
+        <v>322.8899188506768</v>
       </c>
       <c r="D83" s="162" t="n">
         <v>363.4055394295765</v>
       </c>
       <c r="E83" s="162" t="n">
-        <v>402.1199643291073</v>
+        <v>402.1199643291072</v>
       </c>
       <c r="F83" s="162" t="n">
-        <v>443.4653462752644</v>
+        <v>443.4653462752643</v>
       </c>
       <c r="G83" s="163" t="n">
-        <v>479.0016760308992</v>
+        <v>479.0016760308991</v>
       </c>
       <c r="H83" s="161" t="n">
-        <v>30.23444099199677</v>
+        <v>30.23444099199676</v>
       </c>
       <c r="I83" s="162" t="n">
         <v>35.49521111275638</v>
       </c>
       <c r="J83" s="162" t="n">
-        <v>40.12548082108128</v>
+        <v>40.12548082108127</v>
       </c>
       <c r="K83" s="162" t="n">
-        <v>46.72594973961282</v>
+        <v>46.72594973961281</v>
       </c>
       <c r="L83" s="163" t="n">
-        <v>51.88839738708224</v>
+        <v>51.88839738708223</v>
       </c>
       <c r="M83" s="164" t="n">
-        <v>15006213.96924755</v>
+        <v>15006213.96924754</v>
       </c>
       <c r="N83" s="165" t="n">
         <v>18112446.39561063</v>
       </c>
       <c r="O83" s="165" t="n">
-        <v>20850788.61358628</v>
+        <v>20850788.61358627</v>
       </c>
       <c r="P83" s="165" t="n">
         <v>24528510.59192333</v>
       </c>
       <c r="Q83" s="166" t="n">
-        <v>27566067.51104658</v>
+        <v>27566067.51104657</v>
       </c>
       <c r="S83" s="42" t="inlineStr">
         <is>
@@ -8718,49 +8718,49 @@
         </is>
       </c>
       <c r="T83" s="161" t="n">
-        <v>437.1648345841136</v>
+        <v>437.1648345841135</v>
       </c>
       <c r="U83" s="162" t="n">
         <v>491.5040309115609</v>
       </c>
       <c r="V83" s="162" t="n">
-        <v>543.1176011997078</v>
+        <v>543.1176011997077</v>
       </c>
       <c r="W83" s="162" t="n">
-        <v>598.1851927991029</v>
+        <v>598.1851927991027</v>
       </c>
       <c r="X83" s="163" t="n">
         <v>645.2667335856686</v>
       </c>
       <c r="Y83" s="161" t="n">
-        <v>34.58437326351804</v>
+        <v>34.58437326351803</v>
       </c>
       <c r="Z83" s="162" t="n">
         <v>40.62055183953051</v>
       </c>
       <c r="AA83" s="162" t="n">
-        <v>45.93311750611977</v>
+        <v>45.93311750611976</v>
       </c>
       <c r="AB83" s="162" t="n">
-        <v>53.53351139825837</v>
+        <v>53.53351139825836</v>
       </c>
       <c r="AC83" s="163" t="n">
         <v>59.48745649608534</v>
       </c>
       <c r="AD83" s="164" t="n">
-        <v>15006213.96924755</v>
+        <v>15006213.96924754</v>
       </c>
       <c r="AE83" s="165" t="n">
         <v>18112446.39561063</v>
       </c>
       <c r="AF83" s="165" t="n">
-        <v>20850788.61358628</v>
+        <v>20850788.61358627</v>
       </c>
       <c r="AG83" s="165" t="n">
         <v>24528510.59192333</v>
       </c>
       <c r="AH83" s="166" t="n">
-        <v>27566067.51104658</v>
+        <v>27566067.51104657</v>
       </c>
     </row>
     <row r="84" ht="15" customHeight="1" thickBot="1">
@@ -8770,49 +8770,49 @@
         </is>
       </c>
       <c r="C84" s="155" t="n">
-        <v>3919.434024576821</v>
+        <v>3919.434024576819</v>
       </c>
       <c r="D84" s="156" t="n">
-        <v>4369.702217990103</v>
+        <v>4369.702217990101</v>
       </c>
       <c r="E84" s="156" t="n">
-        <v>4506.775808984617</v>
+        <v>4506.775808984615</v>
       </c>
       <c r="F84" s="156" t="n">
-        <v>4996.72203479779</v>
+        <v>4996.722034797789</v>
       </c>
       <c r="G84" s="157" t="n">
-        <v>5464.905209402666</v>
+        <v>5464.905209402663</v>
       </c>
       <c r="H84" s="155" t="n">
-        <v>3904.776103298146</v>
+        <v>3904.776103298145</v>
       </c>
       <c r="I84" s="156" t="n">
-        <v>4349.931263629667</v>
+        <v>4349.931263629665</v>
       </c>
       <c r="J84" s="156" t="n">
-        <v>4192.452133737689</v>
+        <v>4192.452133737686</v>
       </c>
       <c r="K84" s="156" t="n">
         <v>4582.362546449443</v>
       </c>
       <c r="L84" s="157" t="n">
-        <v>5023.739764722726</v>
+        <v>5023.739764722724</v>
       </c>
       <c r="M84" s="158" t="n">
-        <v>1955651.877544766</v>
+        <v>1955651.877544765</v>
       </c>
       <c r="N84" s="159" t="n">
-        <v>2324578.093284687</v>
+        <v>2324578.093284686</v>
       </c>
       <c r="O84" s="159" t="n">
-        <v>2508722.936134457</v>
+        <v>2508722.936134456</v>
       </c>
       <c r="P84" s="159" t="n">
-        <v>2942354.225595081</v>
+        <v>2942354.22559508</v>
       </c>
       <c r="Q84" s="160" t="n">
-        <v>3478863.919009374</v>
+        <v>3478863.919009373</v>
       </c>
       <c r="S84" s="32" t="inlineStr">
         <is>
@@ -8820,49 +8820,49 @@
         </is>
       </c>
       <c r="T84" s="155" t="n">
-        <v>3203.523410313504</v>
+        <v>3203.523410313503</v>
       </c>
       <c r="U84" s="156" t="n">
-        <v>3571.547132482104</v>
+        <v>3571.547132482102</v>
       </c>
       <c r="V84" s="156" t="n">
-        <v>3683.58332314973</v>
+        <v>3683.583323149727</v>
       </c>
       <c r="W84" s="156" t="n">
-        <v>4084.037621996285</v>
+        <v>4084.037621996284</v>
       </c>
       <c r="X84" s="157" t="n">
-        <v>4466.704035248017</v>
+        <v>4466.704035248015</v>
       </c>
       <c r="Y84" s="155" t="n">
-        <v>3193.724489677018</v>
+        <v>3193.724489677016</v>
       </c>
       <c r="Z84" s="156" t="n">
-        <v>3558.3282181686</v>
+        <v>3558.328218168599</v>
       </c>
       <c r="AA84" s="156" t="n">
-        <v>3470.889760971372</v>
+        <v>3470.88976097137</v>
       </c>
       <c r="AB84" s="156" t="n">
-        <v>3802.96730902195</v>
+        <v>3802.967309021949</v>
       </c>
       <c r="AC84" s="157" t="n">
-        <v>4167.572589383496</v>
+        <v>4167.572589383494</v>
       </c>
       <c r="AD84" s="158" t="n">
-        <v>1955651.877544766</v>
+        <v>1955651.877544765</v>
       </c>
       <c r="AE84" s="159" t="n">
-        <v>2324578.093284687</v>
+        <v>2324578.093284686</v>
       </c>
       <c r="AF84" s="159" t="n">
-        <v>2508722.936134457</v>
+        <v>2508722.936134456</v>
       </c>
       <c r="AG84" s="159" t="n">
-        <v>2942354.225595081</v>
+        <v>2942354.22559508</v>
       </c>
       <c r="AH84" s="160" t="n">
-        <v>3478863.919009374</v>
+        <v>3478863.919009373</v>
       </c>
     </row>
     <row r="85" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -8872,34 +8872,34 @@
         </is>
       </c>
       <c r="C85" s="179" t="n">
-        <v>361.0930625564805</v>
+        <v>361.0930625564803</v>
       </c>
       <c r="D85" s="180" t="n">
         <v>405.7151431990948</v>
       </c>
       <c r="E85" s="180" t="n">
-        <v>445.7172198511875</v>
+        <v>445.7172198511873</v>
       </c>
       <c r="F85" s="180" t="n">
-        <v>491.4299900966727</v>
+        <v>491.4299900966726</v>
       </c>
       <c r="G85" s="181" t="n">
         <v>533.5502360688265</v>
       </c>
       <c r="H85" s="179" t="n">
-        <v>34.14022784018511</v>
+        <v>34.1402278401851</v>
       </c>
       <c r="I85" s="180" t="n">
         <v>40.00881925161222</v>
       </c>
       <c r="J85" s="180" t="n">
-        <v>44.90158772589582</v>
+        <v>44.9015877258958</v>
       </c>
       <c r="K85" s="180" t="n">
-        <v>52.26709864592003</v>
+        <v>52.26709864592002</v>
       </c>
       <c r="L85" s="181" t="n">
-        <v>58.36069021905488</v>
+        <v>58.36069021905487</v>
       </c>
       <c r="M85" s="182" t="n">
         <v>16961865.84679231</v>
@@ -8922,19 +8922,19 @@
         </is>
       </c>
       <c r="T85" s="185" t="n">
-        <v>485.5030309315443</v>
+        <v>485.5030309315442</v>
       </c>
       <c r="U85" s="186" t="n">
         <v>544.9593589534441</v>
       </c>
       <c r="V85" s="186" t="n">
-        <v>597.8583593976582</v>
+        <v>597.858359397658</v>
       </c>
       <c r="W85" s="186" t="n">
-        <v>658.3738203647395</v>
+        <v>658.3738203647393</v>
       </c>
       <c r="X85" s="187" t="n">
-        <v>713.6886244901152</v>
+        <v>713.6886244901151</v>
       </c>
       <c r="Y85" s="185" t="n">
         <v>39.03641574691967</v>
@@ -8943,13 +8943,13 @@
         <v>45.76680052004828</v>
       </c>
       <c r="AA85" s="186" t="n">
-        <v>51.3778861814661</v>
+        <v>51.37788618146607</v>
       </c>
       <c r="AB85" s="186" t="n">
-        <v>59.85413421618061</v>
+        <v>59.8541342161806</v>
       </c>
       <c r="AC85" s="187" t="n">
-        <v>66.87436403579053</v>
+        <v>66.87436403579052</v>
       </c>
       <c r="AD85" s="188" t="n">
         <v>16961865.84679231</v>
@@ -9868,19 +9868,19 @@
         </is>
       </c>
       <c r="C95" s="79" t="n">
-        <v>498.9628260819919</v>
+        <v>498.962826081992</v>
       </c>
       <c r="D95" s="80" t="n">
         <v>531.9763172223448</v>
       </c>
       <c r="E95" s="80" t="n">
-        <v>556.6558094887075</v>
+        <v>556.6558094887076</v>
       </c>
       <c r="F95" s="80" t="n">
         <v>588.8568956015889</v>
       </c>
       <c r="G95" s="81" t="n">
-        <v>636.5826644209308</v>
+        <v>636.5826644209309</v>
       </c>
       <c r="H95" s="79" t="n">
         <v>1.87302873</v>
@@ -9898,19 +9898,19 @@
         <v>55.90223367</v>
       </c>
       <c r="M95" s="79" t="n">
-        <v>500.8358548119919</v>
+        <v>500.835854811992</v>
       </c>
       <c r="N95" s="80" t="n">
         <v>534.3942127823449</v>
       </c>
       <c r="O95" s="80" t="n">
-        <v>598.3903586987075</v>
+        <v>598.3903586987076</v>
       </c>
       <c r="P95" s="80" t="n">
         <v>642.1041975115889</v>
       </c>
       <c r="Q95" s="81" t="n">
-        <v>692.4848980909308</v>
+        <v>692.4848980909309</v>
       </c>
       <c r="S95" s="32" t="inlineStr">
         <is>
@@ -9918,19 +9918,19 @@
         </is>
       </c>
       <c r="T95" s="79" t="n">
-        <v>610.469045192144</v>
+        <v>610.4690451921441</v>
       </c>
       <c r="U95" s="80" t="n">
         <v>650.8602594498547</v>
       </c>
       <c r="V95" s="80" t="n">
-        <v>681.0550260579738</v>
+        <v>681.055026057974</v>
       </c>
       <c r="W95" s="80" t="n">
         <v>720.452282258079</v>
       </c>
       <c r="X95" s="81" t="n">
-        <v>778.8436152376966</v>
+        <v>778.8436152376967</v>
       </c>
       <c r="Y95" s="79" t="n">
         <v>1.87302873</v>
@@ -9948,19 +9948,19 @@
         <v>55.90223367</v>
       </c>
       <c r="AD95" s="79" t="n">
-        <v>612.342073922144</v>
+        <v>612.3420739221441</v>
       </c>
       <c r="AE95" s="80" t="n">
         <v>653.2781550098547</v>
       </c>
       <c r="AF95" s="80" t="n">
-        <v>722.7895752679738</v>
+        <v>722.789575267974</v>
       </c>
       <c r="AG95" s="80" t="n">
         <v>773.699584168079</v>
       </c>
       <c r="AH95" s="81" t="n">
-        <v>834.7458489076965</v>
+        <v>834.7458489076967</v>
       </c>
       <c r="AJ95" s="120" t="n">
         <v>36.70428015564202</v>
